--- a/public/LinearModule.xlsx
+++ b/public/LinearModule.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ru0nntr\Desktop\Прочее\Linear Motion Calculator\project_v0.95\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ru0nntr\Desktop\Прочее\Linear Motion Calculator\project_v0.96\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="61">
   <si>
     <t>ITO40</t>
   </si>
@@ -171,13 +171,49 @@
   </si>
   <si>
     <t>Screw_la</t>
+  </si>
+  <si>
+    <t>mod_Mx</t>
+  </si>
+  <si>
+    <t>mod_My</t>
+  </si>
+  <si>
+    <t>mod_Mz</t>
+  </si>
+  <si>
+    <t>mod_lever</t>
+  </si>
+  <si>
+    <t>mod_GSLM</t>
+  </si>
+  <si>
+    <t>mod_Zd</t>
+  </si>
+  <si>
+    <t>mod_pic</t>
+  </si>
+  <si>
+    <t>https://smarta.ru/upload/resize_cache/iblock/040/ep8pn4jto5au0a5ymsd3p326uxudj5l1/649_393_2/ITC.png</t>
+  </si>
+  <si>
+    <t>https://smarta.ru/upload/resize_cache/iblock/2d4/8bltm7c7edndleb5qt6ap06fmouw9q4g/618_452_2/GTC_80_SMARTA.png</t>
+  </si>
+  <si>
+    <t>https://smarta.ru/upload/resize_cache/iblock/8d0/wnxrj1xo08hboz7v7dk8rcfiu1s3v1sl/682_408_2/GSC_50_80.png</t>
+  </si>
+  <si>
+    <t>https://smarta.ru/upload/resize_cache/iblock/28b/hh11io00vis73zwwkng3i5lkrida2emb/1000_650_2/GSC_120.png</t>
+  </si>
+  <si>
+    <t>https://smarta.ru/upload/iblock/2b1/ynpg6ux0t9ui36qgk8qsfz9vrs3hsqsp/LMC_S_1.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,6 +221,11 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -204,13 +245,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Standard 2" xfId="1"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -489,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -498,7 +541,7 @@
     <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -526,8 +569,29 @@
       <c r="I1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -555,8 +619,29 @@
       <c r="I2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>33</v>
+      </c>
+      <c r="N2">
+        <v>5000</v>
+      </c>
+      <c r="O2">
+        <v>20</v>
+      </c>
+      <c r="P2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -584,8 +669,29 @@
       <c r="I3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>22</v>
+      </c>
+      <c r="K3">
+        <v>78</v>
+      </c>
+      <c r="L3">
+        <v>78</v>
+      </c>
+      <c r="M3">
+        <v>60</v>
+      </c>
+      <c r="N3">
+        <v>10000</v>
+      </c>
+      <c r="O3">
+        <v>40</v>
+      </c>
+      <c r="P3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -613,8 +719,29 @@
       <c r="I4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <v>75</v>
+      </c>
+      <c r="K4">
+        <v>210</v>
+      </c>
+      <c r="L4">
+        <v>210</v>
+      </c>
+      <c r="M4">
+        <v>76</v>
+      </c>
+      <c r="N4">
+        <v>1250</v>
+      </c>
+      <c r="O4">
+        <v>50</v>
+      </c>
+      <c r="P4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -642,8 +769,29 @@
       <c r="I5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <v>115</v>
+      </c>
+      <c r="K5">
+        <v>310</v>
+      </c>
+      <c r="L5">
+        <v>310</v>
+      </c>
+      <c r="M5">
+        <v>95</v>
+      </c>
+      <c r="N5">
+        <v>1500</v>
+      </c>
+      <c r="O5">
+        <v>65</v>
+      </c>
+      <c r="P5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -671,8 +819,29 @@
       <c r="I6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <v>395.1</v>
+      </c>
+      <c r="K6">
+        <v>356.2</v>
+      </c>
+      <c r="L6">
+        <v>348.8</v>
+      </c>
+      <c r="M6">
+        <v>60</v>
+      </c>
+      <c r="N6">
+        <v>7500</v>
+      </c>
+      <c r="O6">
+        <v>40</v>
+      </c>
+      <c r="P6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -701,8 +870,29 @@
       <c r="I7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <v>12.6</v>
+      </c>
+      <c r="K7">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="L7">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="M7">
+        <v>40</v>
+      </c>
+      <c r="N7">
+        <v>10000</v>
+      </c>
+      <c r="O7">
+        <v>30</v>
+      </c>
+      <c r="P7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -731,8 +921,29 @@
       <c r="I8">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <v>12.6</v>
+      </c>
+      <c r="K8">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="L8">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="M8">
+        <v>40</v>
+      </c>
+      <c r="N8">
+        <v>10000</v>
+      </c>
+      <c r="O8">
+        <v>30</v>
+      </c>
+      <c r="P8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -761,8 +972,29 @@
       <c r="I9">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <v>12.6</v>
+      </c>
+      <c r="K9">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="L9">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="M9">
+        <v>40</v>
+      </c>
+      <c r="N9">
+        <v>10000</v>
+      </c>
+      <c r="O9">
+        <v>30</v>
+      </c>
+      <c r="P9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -790,8 +1022,29 @@
       <c r="I10">
         <v>125</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <v>43.5</v>
+      </c>
+      <c r="K10">
+        <v>26.2</v>
+      </c>
+      <c r="L10">
+        <v>26.2</v>
+      </c>
+      <c r="M10">
+        <v>50</v>
+      </c>
+      <c r="N10">
+        <v>10000</v>
+      </c>
+      <c r="O10">
+        <v>40</v>
+      </c>
+      <c r="P10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -819,8 +1072,29 @@
       <c r="I11">
         <v>125</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11">
+        <v>43.5</v>
+      </c>
+      <c r="K11">
+        <v>26.2</v>
+      </c>
+      <c r="L11">
+        <v>26.2</v>
+      </c>
+      <c r="M11">
+        <v>50</v>
+      </c>
+      <c r="N11">
+        <v>10000</v>
+      </c>
+      <c r="O11">
+        <v>40</v>
+      </c>
+      <c r="P11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -848,8 +1122,29 @@
       <c r="I12">
         <v>125</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12">
+        <v>43.5</v>
+      </c>
+      <c r="K12">
+        <v>26.2</v>
+      </c>
+      <c r="L12">
+        <v>26.2</v>
+      </c>
+      <c r="M12">
+        <v>50</v>
+      </c>
+      <c r="N12">
+        <v>10000</v>
+      </c>
+      <c r="O12">
+        <v>40</v>
+      </c>
+      <c r="P12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -877,8 +1172,29 @@
       <c r="I13">
         <v>125</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <v>43.5</v>
+      </c>
+      <c r="K13">
+        <v>26.2</v>
+      </c>
+      <c r="L13">
+        <v>26.2</v>
+      </c>
+      <c r="M13">
+        <v>50</v>
+      </c>
+      <c r="N13">
+        <v>10000</v>
+      </c>
+      <c r="O13">
+        <v>40</v>
+      </c>
+      <c r="P13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -906,8 +1222,29 @@
       <c r="I14">
         <v>125</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <v>233.4</v>
+      </c>
+      <c r="K14">
+        <v>129.69999999999999</v>
+      </c>
+      <c r="L14">
+        <v>129.69999999999999</v>
+      </c>
+      <c r="M14">
+        <v>50</v>
+      </c>
+      <c r="N14">
+        <v>10000</v>
+      </c>
+      <c r="O14">
+        <v>35</v>
+      </c>
+      <c r="P14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -935,8 +1272,29 @@
       <c r="I15">
         <v>125</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <v>233.4</v>
+      </c>
+      <c r="K15">
+        <v>129.69999999999999</v>
+      </c>
+      <c r="L15">
+        <v>129.69999999999999</v>
+      </c>
+      <c r="M15">
+        <v>50</v>
+      </c>
+      <c r="N15">
+        <v>10000</v>
+      </c>
+      <c r="O15">
+        <v>35</v>
+      </c>
+      <c r="P15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -964,8 +1322,29 @@
       <c r="I16">
         <v>125</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <v>233.4</v>
+      </c>
+      <c r="K16">
+        <v>129.69999999999999</v>
+      </c>
+      <c r="L16">
+        <v>129.69999999999999</v>
+      </c>
+      <c r="M16">
+        <v>50</v>
+      </c>
+      <c r="N16">
+        <v>10000</v>
+      </c>
+      <c r="O16">
+        <v>35</v>
+      </c>
+      <c r="P16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -993,8 +1372,29 @@
       <c r="I17">
         <v>125</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <v>233.4</v>
+      </c>
+      <c r="K17">
+        <v>129.69999999999999</v>
+      </c>
+      <c r="L17">
+        <v>129.69999999999999</v>
+      </c>
+      <c r="M17">
+        <v>50</v>
+      </c>
+      <c r="N17">
+        <v>10000</v>
+      </c>
+      <c r="O17">
+        <v>35</v>
+      </c>
+      <c r="P17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1022,8 +1422,29 @@
       <c r="I18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <v>12.6</v>
+      </c>
+      <c r="K18">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="L18">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="M18">
+        <v>40</v>
+      </c>
+      <c r="N18">
+        <v>10000</v>
+      </c>
+      <c r="O18">
+        <v>30</v>
+      </c>
+      <c r="P18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1051,8 +1472,29 @@
       <c r="I19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19">
+        <v>43.5</v>
+      </c>
+      <c r="K19">
+        <v>26.2</v>
+      </c>
+      <c r="L19">
+        <v>26.2</v>
+      </c>
+      <c r="M19">
+        <v>50</v>
+      </c>
+      <c r="N19">
+        <v>10000</v>
+      </c>
+      <c r="O19">
+        <v>40</v>
+      </c>
+      <c r="P19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1081,8 +1523,29 @@
       <c r="I20">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1111,8 +1574,29 @@
       <c r="I21">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1141,8 +1625,29 @@
       <c r="I22">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1171,8 +1676,29 @@
       <c r="I23">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1201,8 +1727,29 @@
       <c r="I24">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1231,8 +1778,29 @@
       <c r="I25">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1261,8 +1829,29 @@
       <c r="I26">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1291,8 +1880,29 @@
       <c r="I27">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1321,8 +1931,29 @@
       <c r="I28">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -1350,8 +1981,29 @@
       <c r="I29">
         <v>125</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -1379,8 +2031,29 @@
       <c r="I30">
         <v>125</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -1408,8 +2081,29 @@
       <c r="I31">
         <v>125</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -1438,8 +2132,29 @@
       <c r="I32">
         <v>150</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -1468,8 +2183,29 @@
       <c r="I33">
         <v>150</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -1498,8 +2234,29 @@
       <c r="I34">
         <v>150</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1528,8 +2285,29 @@
       <c r="I35">
         <v>200</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1552,14 +2330,35 @@
         <v>19930</v>
       </c>
       <c r="H36">
-        <f t="shared" ref="H36:H38" si="3">32-3.969</f>
+        <f t="shared" ref="H36:H37" si="3">32-3.969</f>
         <v>28.030999999999999</v>
       </c>
       <c r="I36">
         <v>200</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1588,8 +2387,29 @@
       <c r="I37">
         <v>200</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1618,8 +2438,29 @@
       <c r="I38">
         <v>175</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -1648,8 +2489,29 @@
       <c r="I39">
         <v>225</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -1678,8 +2540,29 @@
       <c r="I40">
         <v>225</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1707,6 +2590,27 @@
       </c>
       <c r="I41">
         <v>225</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/public/LinearModule.xlsx
+++ b/public/LinearModule.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="63">
   <si>
     <t>ITO40</t>
   </si>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>https://smarta.ru/upload/iblock/2b1/ynpg6ux0t9ui36qgk8qsfz9vrs3hsqsp/LMC_S_1.png</t>
+  </si>
+  <si>
+    <t>mod_maxSpeed</t>
+  </si>
+  <si>
+    <t>mod_maxAcc</t>
   </si>
 </sst>
 </file>
@@ -532,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -541,7 +547,7 @@
     <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -590,8 +596,14 @@
       <c r="P1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>61</v>
+      </c>
+      <c r="R1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -640,8 +652,14 @@
       <c r="P2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <v>3</v>
+      </c>
+      <c r="R2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -690,8 +708,14 @@
       <c r="P3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <v>5</v>
+      </c>
+      <c r="R3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -740,8 +764,14 @@
       <c r="P4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <v>5</v>
+      </c>
+      <c r="R4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -790,8 +820,14 @@
       <c r="P5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <v>5</v>
+      </c>
+      <c r="R5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -840,8 +876,14 @@
       <c r="P6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <v>5</v>
+      </c>
+      <c r="R6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -891,8 +933,14 @@
       <c r="P7" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <v>0.25</v>
+      </c>
+      <c r="R7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -942,8 +990,14 @@
       <c r="P8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <v>0.5</v>
+      </c>
+      <c r="R8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -993,8 +1047,14 @@
       <c r="P9" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1043,8 +1103,14 @@
       <c r="P10" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <v>0.25</v>
+      </c>
+      <c r="R10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1093,8 +1159,14 @@
       <c r="P11" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <v>0.5</v>
+      </c>
+      <c r="R11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1143,8 +1215,14 @@
       <c r="P12" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1193,8 +1271,14 @@
       <c r="P13" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q13">
+        <v>1.6</v>
+      </c>
+      <c r="R13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1243,8 +1327,14 @@
       <c r="P14" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q14">
+        <v>0.25</v>
+      </c>
+      <c r="R14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1293,8 +1383,14 @@
       <c r="P15" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q15">
+        <v>0.5</v>
+      </c>
+      <c r="R15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1343,8 +1439,14 @@
       <c r="P16" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1393,8 +1495,14 @@
       <c r="P17" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q17">
+        <v>1.6</v>
+      </c>
+      <c r="R17">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1443,8 +1551,14 @@
       <c r="P18" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q18">
+        <v>2</v>
+      </c>
+      <c r="R18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1493,8 +1607,14 @@
       <c r="P19" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q19">
+        <v>2.4</v>
+      </c>
+      <c r="R19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1511,7 +1631,7 @@
         <v>5.2300000000000004E-5</v>
       </c>
       <c r="F20">
-        <v>1.29112220106376</v>
+        <v>1.17</v>
       </c>
       <c r="G20">
         <v>5380</v>
@@ -1544,8 +1664,14 @@
       <c r="P20" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q20">
+        <v>0.25</v>
+      </c>
+      <c r="R20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1595,8 +1721,14 @@
       <c r="P21" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q21">
+        <v>0.5</v>
+      </c>
+      <c r="R21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1646,8 +1778,14 @@
       <c r="P22" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1664,7 +1802,7 @@
         <v>5.2300000000000004E-5</v>
       </c>
       <c r="F23">
-        <v>1.29112220106376</v>
+        <v>1.17</v>
       </c>
       <c r="G23">
         <v>5380</v>
@@ -1697,8 +1835,14 @@
       <c r="P23" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q23">
+        <v>0.25</v>
+      </c>
+      <c r="R23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1748,8 +1892,14 @@
       <c r="P24" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q24">
+        <v>0.5</v>
+      </c>
+      <c r="R24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1799,8 +1949,14 @@
       <c r="P25" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1817,7 +1973,7 @@
         <v>5.2300000000000004E-5</v>
       </c>
       <c r="F26">
-        <v>1.29112220106376</v>
+        <v>1.17</v>
       </c>
       <c r="G26">
         <v>5380</v>
@@ -1850,8 +2006,14 @@
       <c r="P26" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q26">
+        <v>0.25</v>
+      </c>
+      <c r="R26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1901,8 +2063,14 @@
       <c r="P27" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q27">
+        <v>0.5</v>
+      </c>
+      <c r="R27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1952,8 +2120,14 @@
       <c r="P28" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="R28">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -1970,7 +2144,7 @@
         <v>1.139E-4</v>
       </c>
       <c r="F29">
-        <v>2.1283406658349202</v>
+        <v>2.67</v>
       </c>
       <c r="G29">
         <v>8870</v>
@@ -2002,8 +2176,14 @@
       <c r="P29" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q29">
+        <v>0.25</v>
+      </c>
+      <c r="R29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -2020,7 +2200,7 @@
         <v>1.139E-4</v>
       </c>
       <c r="F30">
-        <v>4.1483354126994554</v>
+        <v>5.07</v>
       </c>
       <c r="G30">
         <v>6860</v>
@@ -2052,8 +2232,14 @@
       <c r="P30" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q30">
+        <v>0.5</v>
+      </c>
+      <c r="R30">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -2070,7 +2256,7 @@
         <v>1.139E-4</v>
       </c>
       <c r="F31">
-        <v>7.3281239739969797</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="G31">
         <v>4810</v>
@@ -2102,8 +2288,14 @@
       <c r="P31" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q31">
+        <v>1</v>
+      </c>
+      <c r="R31">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -2120,7 +2312,7 @@
         <v>3.0499999999999999E-4</v>
       </c>
       <c r="F32">
-        <v>2.8818372841289648</v>
+        <v>3.96</v>
       </c>
       <c r="G32">
         <v>12010</v>
@@ -2153,8 +2345,14 @@
       <c r="P32" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q32">
+        <v>0.25</v>
+      </c>
+      <c r="R32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -2171,7 +2369,7 @@
         <v>3.0499999999999999E-4</v>
       </c>
       <c r="F33">
-        <v>7.2920086676735183</v>
+        <v>9.91</v>
       </c>
       <c r="G33">
         <v>12060</v>
@@ -2204,8 +2402,14 @@
       <c r="P33" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q33">
+        <v>0.5</v>
+      </c>
+      <c r="R33">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -2222,7 +2426,7 @@
         <v>3.0499999999999999E-4</v>
       </c>
       <c r="F34">
-        <v>14.337776610414343</v>
+        <v>16.97</v>
       </c>
       <c r="G34">
         <v>9410</v>
@@ -2255,8 +2459,14 @@
       <c r="P34" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q34">
+        <v>1</v>
+      </c>
+      <c r="R34">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -2273,7 +2483,7 @@
         <v>8.2799999999999996E-4</v>
       </c>
       <c r="F35">
-        <v>6.0263313415194695</v>
+        <v>29.06</v>
       </c>
       <c r="G35">
         <v>14640</v>
@@ -2306,8 +2516,14 @@
       <c r="P35" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q35">
+        <v>0.25</v>
+      </c>
+      <c r="R35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -2324,7 +2540,7 @@
         <v>8.2799999999999996E-4</v>
       </c>
       <c r="F36">
-        <v>12.052662683038939</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="G36">
         <v>19930</v>
@@ -2357,8 +2573,14 @@
       <c r="P36" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q36">
+        <v>0.5</v>
+      </c>
+      <c r="R36">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -2375,7 +2597,7 @@
         <v>8.2799999999999996E-4</v>
       </c>
       <c r="F37">
-        <v>23.49793157791057</v>
+        <v>49.79</v>
       </c>
       <c r="G37">
         <v>15420</v>
@@ -2408,8 +2630,14 @@
       <c r="P37" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q37">
+        <v>1</v>
+      </c>
+      <c r="R37">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -2426,7 +2654,7 @@
         <v>3.0499999999999999E-4</v>
       </c>
       <c r="F38">
-        <v>21.193118392540548</v>
+        <v>36.380000000000003</v>
       </c>
       <c r="G38">
         <v>10330</v>
@@ -2459,8 +2687,14 @@
       <c r="P38" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q38">
+        <v>1.2</v>
+      </c>
+      <c r="R38">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -2477,7 +2711,7 @@
         <v>2.0400000000000001E-3</v>
       </c>
       <c r="F39">
-        <v>25.3</v>
+        <v>32.65</v>
       </c>
       <c r="G39">
         <v>41830</v>
@@ -2510,8 +2744,14 @@
       <c r="P39" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q39">
+        <v>0.5</v>
+      </c>
+      <c r="R39">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -2528,7 +2768,7 @@
         <v>2.0400000000000001E-3</v>
       </c>
       <c r="F40">
-        <v>49.21</v>
+        <v>55.94</v>
       </c>
       <c r="G40">
         <v>32290</v>
@@ -2561,8 +2801,14 @@
       <c r="P40" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q40">
+        <v>1</v>
+      </c>
+      <c r="R40">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -2611,6 +2857,12 @@
       </c>
       <c r="P41" t="s">
         <v>60</v>
+      </c>
+      <c r="Q41">
+        <v>2</v>
+      </c>
+      <c r="R41">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/public/LinearModule.xlsx
+++ b/public/LinearModule.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ru0nntr\Desktop\Прочее\Linear Motion Calculator\project_v0.96\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ru0nntr\Desktop\Прочее\Linear Motion Calculator\project_v0.97\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1498,7 +1498,7 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>0.4</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D17">
         <v>1.5E-6</v>
@@ -1555,7 +1555,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="D18">
         <v>1.5E-6</v>
@@ -1612,7 +1612,7 @@
         <v>20</v>
       </c>
       <c r="C19">
-        <v>0.4</v>
+        <v>0.09</v>
       </c>
       <c r="D19">
         <v>1.5E-6</v>
@@ -1669,7 +1669,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
       <c r="D20">
         <v>9.9999999999999991E-6</v>
@@ -1725,7 +1725,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.75</v>
+        <v>0.12</v>
       </c>
       <c r="D21">
         <v>9.9999999999999991E-6</v>
@@ -1781,7 +1781,7 @@
         <v>20</v>
       </c>
       <c r="C22">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="D22">
         <v>9.9999999999999991E-6</v>
@@ -1837,7 +1837,7 @@
         <v>32</v>
       </c>
       <c r="C23">
-        <v>0.75</v>
+        <v>0.17</v>
       </c>
       <c r="D23">
         <v>9.9999999999999991E-6</v>
@@ -1893,7 +1893,7 @@
         <v>5</v>
       </c>
       <c r="C24">
-        <v>1.3</v>
+        <v>0.12</v>
       </c>
       <c r="D24">
         <v>6.4459999999999989E-5</v>
@@ -1949,7 +1949,7 @@
         <v>10</v>
       </c>
       <c r="C25">
-        <v>1.3</v>
+        <v>0.15</v>
       </c>
       <c r="D25">
         <v>6.4459999999999989E-5</v>
@@ -2005,7 +2005,7 @@
         <v>20</v>
       </c>
       <c r="C26">
-        <v>1.3</v>
+        <v>0.17</v>
       </c>
       <c r="D26">
         <v>6.4459999999999989E-5</v>
@@ -2061,7 +2061,7 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>1.3</v>
+        <v>0.19</v>
       </c>
       <c r="D27">
         <v>6.4459999999999989E-5</v>

--- a/public/LinearModule.xlsx
+++ b/public/LinearModule.xlsx
@@ -185,21 +185,6 @@
     <t>mod_pic</t>
   </si>
   <si>
-    <t>https://smarta.ru/upload/resize_cache/iblock/040/ep8pn4jto5au0a5ymsd3p326uxudj5l1/649_393_2/ITC.png</t>
-  </si>
-  <si>
-    <t>https://smarta.ru/upload/resize_cache/iblock/2d4/8bltm7c7edndleb5qt6ap06fmouw9q4g/618_452_2/GTC_80_SMARTA.png</t>
-  </si>
-  <si>
-    <t>https://smarta.ru/upload/resize_cache/iblock/8d0/wnxrj1xo08hboz7v7dk8rcfiu1s3v1sl/682_408_2/GSC_50_80.png</t>
-  </si>
-  <si>
-    <t>https://smarta.ru/upload/resize_cache/iblock/28b/hh11io00vis73zwwkng3i5lkrida2emb/1000_650_2/GSC_120.png</t>
-  </si>
-  <si>
-    <t>https://smarta.ru/upload/iblock/2b1/ynpg6ux0t9ui36qgk8qsfz9vrs3hsqsp/LMC_S_1.png</t>
-  </si>
-  <si>
     <t>mod_maxSpeed</t>
   </si>
   <si>
@@ -245,13 +230,28 @@
     <t>HTZ80</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/cLTHzQ7y/ITO160.png</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/pLkTSDQt/HTZ60-80.png</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/g24J7vVt/HTO60-80-100.png</t>
+    <t>./pics/itc.png</t>
+  </si>
+  <si>
+    <t>./pics/ito_160.png</t>
+  </si>
+  <si>
+    <t>./pics/hto.png</t>
+  </si>
+  <si>
+    <t>./pics/htz-60_80.png</t>
+  </si>
+  <si>
+    <t>./pics/gsc-50_80.png</t>
+  </si>
+  <si>
+    <t>./pics/gsc-120.png</t>
+  </si>
+  <si>
+    <t>./pics/gtc.png</t>
+  </si>
+  <si>
+    <t>./pics/lmc.png</t>
   </si>
 </sst>
 </file>
@@ -636,10 +636,10 @@
         <v>52</v>
       </c>
       <c r="Q1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="R1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -689,7 +689,7 @@
         <v>20</v>
       </c>
       <c r="P2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="Q2">
         <v>3</v>
@@ -700,7 +700,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B3">
         <v>130</v>
@@ -745,7 +745,7 @@
         <v>40</v>
       </c>
       <c r="P3" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B4">
         <v>130</v>
@@ -802,7 +802,7 @@
         <v>40</v>
       </c>
       <c r="P4" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -813,7 +813,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B5">
         <v>176</v>
@@ -858,7 +858,7 @@
         <v>50</v>
       </c>
       <c r="P5" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B6">
         <v>176</v>
@@ -915,7 +915,7 @@
         <v>50</v>
       </c>
       <c r="P6" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -926,7 +926,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B7">
         <v>224</v>
@@ -971,7 +971,7 @@
         <v>65</v>
       </c>
       <c r="P7" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -982,7 +982,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B8">
         <v>224</v>
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="P8" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -1084,7 +1084,7 @@
         <v>40</v>
       </c>
       <c r="P9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B10">
         <v>130</v>
@@ -1140,7 +1140,7 @@
         <v>40</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -1151,7 +1151,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B11">
         <v>176</v>
@@ -1196,7 +1196,7 @@
         <v>50</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B12">
         <v>176</v>
@@ -1253,7 +1253,7 @@
         <v>50</v>
       </c>
       <c r="P12" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Q12">
         <v>5</v>
@@ -1264,7 +1264,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B13">
         <v>224</v>
@@ -1309,7 +1309,7 @@
         <v>65</v>
       </c>
       <c r="P13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -1320,7 +1320,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <v>224</v>
@@ -1366,7 +1366,7 @@
         <v>65</v>
       </c>
       <c r="P14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Q14">
         <v>5</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B15">
         <v>130</v>
@@ -1423,7 +1423,7 @@
         <v>40</v>
       </c>
       <c r="P15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B16">
         <v>210</v>
@@ -1481,7 +1481,7 @@
         <v>50</v>
       </c>
       <c r="P16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q16">
         <v>5</v>
@@ -1538,7 +1538,7 @@
         <v>30</v>
       </c>
       <c r="P17" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="Q17">
         <v>0.25</v>
@@ -1595,7 +1595,7 @@
         <v>30</v>
       </c>
       <c r="P18" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="Q18">
         <v>0.5</v>
@@ -1652,7 +1652,7 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="Q19">
         <v>1</v>
@@ -1708,7 +1708,7 @@
         <v>40</v>
       </c>
       <c r="P20" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="Q20">
         <v>0.25</v>
@@ -1764,7 +1764,7 @@
         <v>40</v>
       </c>
       <c r="P21" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="Q21">
         <v>0.5</v>
@@ -1820,7 +1820,7 @@
         <v>40</v>
       </c>
       <c r="P22" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="Q22">
         <v>1</v>
@@ -1876,7 +1876,7 @@
         <v>40</v>
       </c>
       <c r="P23" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="Q23">
         <v>1.6</v>
@@ -1932,7 +1932,7 @@
         <v>35</v>
       </c>
       <c r="P24" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="Q24">
         <v>0.25</v>
@@ -1988,7 +1988,7 @@
         <v>35</v>
       </c>
       <c r="P25" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="Q25">
         <v>0.5</v>
@@ -2044,7 +2044,7 @@
         <v>35</v>
       </c>
       <c r="P26" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="Q26">
         <v>1</v>
@@ -2100,7 +2100,7 @@
         <v>35</v>
       </c>
       <c r="P27" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="Q27">
         <v>1.6</v>
@@ -2156,7 +2156,7 @@
         <v>30</v>
       </c>
       <c r="P28" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="Q28">
         <v>2</v>
@@ -2212,7 +2212,7 @@
         <v>40</v>
       </c>
       <c r="P29" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="Q29">
         <v>2.4</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q30">
         <v>0.25</v>
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q31">
         <v>0.5</v>
@@ -2383,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q32">
         <v>1</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q33">
         <v>0.25</v>
@@ -2497,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q34">
         <v>0.5</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q35">
         <v>1</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q36">
         <v>0.25</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q37">
         <v>0.5</v>
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q38">
         <v>1</v>
@@ -2781,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q39">
         <v>0.25</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q40">
         <v>0.5</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q41">
         <v>1</v>
@@ -2950,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q42">
         <v>0.25</v>
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q43">
         <v>0.5</v>
@@ -3064,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q45">
         <v>0.25</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q46">
         <v>0.5</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q47">
         <v>1</v>
@@ -3292,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q48">
         <v>1.2</v>
@@ -3349,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q49">
         <v>0.5</v>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -3463,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="Q51">
         <v>2</v>
